--- a/vlearn-app/public/quiz_excel/Day_15_Triển khai thực tế _ Định hướng Enterprise/Day_15_Phan_01_23_Cau.xlsx
+++ b/vlearn-app/public/quiz_excel/Day_15_Triển khai thực tế _ Định hướng Enterprise/Day_15_Phan_01_23_Cau.xlsx
@@ -1131,7 +1131,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>400</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
@@ -1159,7 +1159,7 @@
       <c r="J13" s="3" t="n"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Hosted TCO=4.000+500+1.200=5.700; self-hosted=3.000+600+2.000+500=6.100; chênh lệch=400 USD/tháng.</t>
+          <t>Hosted TCO: $4.000 + $500 + $1.200 = $5.700. Self-hosted TCO: $3.000 + $600 + $2.000 + $500 = $6.100. Chênh lệch TCO self-hosted trừ hosted: $6.100 - $5.700 = 400 USD/tháng.</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>111111</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -1255,7 +1255,7 @@
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>Điểm hòa vốn TCO: 500 + 0.04*N = 4500 + 0.004*N =&gt; 0.036*N = 4000 =&gt; N = 4000 / 0.036 ≈ 111,111 request/tháng.</t>
+          <t>Break-even volume: 500 + 0,04*N = 4500 + 0,004*N =&gt; 0,036*N = 4000 =&gt; N = 4000 / 0,036 ≈ 111.111 requests/tháng.</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3200</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
@@ -1303,7 +1303,7 @@
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính từng option ở cùng volume trước khi trừ.</t>
+          <t>Tại V = 200.000 requests/tháng: Hosted cost = $500 + $0,04 * 200.000 = $500 + $8.000 = $8.500. Self-hosted cost = $4.500 + $0,004 * 200.000 = $4.500 + $800 = $5.300. Self-hosted rẻ hơn hosted: $8.500 - $5.300 = 3.200 USD/tháng.</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -1471,7 +1471,7 @@
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Per request=$0,002+$0,002=$0,004; 1,5 triệu request/tháng ⇒ $6.000.</t>
+          <t>Mỗi request: 1.000 input tokens * $2/M + 200 output tokens * $10/M = $0,002 + $0,002 = $0,004/request. Hàng tháng có 50.000 * 30 = 1.500.000 requests =&gt; Tổng chi phí: 1.500.000 * $0,004 = 6.000 USD/tháng.</t>
         </is>
       </c>
     </row>
@@ -1491,7 +1491,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1860</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
@@ -1519,7 +1519,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính input và output subtotal riêng trước khi cộng.</t>
+          <t>Tổng API subtotal: (496 triệu input tokens * $1,5 / triệu) + (186 triệu output tokens * $6 / triệu) = 496 * 1,5 + 186 * 6 = $744 + $1.116 = 1.860 USD/tháng.</t>
         </is>
       </c>
     </row>
